--- a/smak-miodu/apka/gotowe.xlsx
+++ b/smak-miodu/apka/gotowe.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>is_taste_ok</t>
+          <t>is_typical</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3110,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -4958,7 +4958,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>1</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -6806,7 +6806,7 @@
         <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>1</v>
       </c>
       <c r="K152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>1</v>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>1</v>
       </c>
       <c r="K166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>1</v>
       </c>
       <c r="K173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -8186,7 +8186,12 @@
         <v>3</v>
       </c>
       <c r="C177" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -8225,7 +8230,12 @@
         <v>2</v>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -8264,7 +8274,12 @@
         <v>3</v>
       </c>
       <c r="C179" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -8303,7 +8318,12 @@
         <v>2</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -8326,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="K180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -8344,6 +8364,11 @@
       <c r="C181" t="n">
         <v>1</v>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>5-cq25111501-1</t>
@@ -8383,6 +8408,11 @@
       <c r="C182" t="n">
         <v>1</v>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>6-02/09</t>
@@ -8417,10 +8447,15 @@
         <v>26</v>
       </c>
       <c r="B183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -8619,7 +8654,7 @@
         <v>1</v>
       </c>
       <c r="K187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -8927,7 +8962,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -9235,7 +9270,7 @@
         <v>1</v>
       </c>
       <c r="K201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -9543,7 +9578,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -9851,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="K215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -10159,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -10467,7 +10502,7 @@
         <v>1</v>
       </c>
       <c r="K229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -10775,7 +10810,7 @@
         <v>1</v>
       </c>
       <c r="K236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -11083,7 +11118,7 @@
         <v>1</v>
       </c>
       <c r="K243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -11391,7 +11426,7 @@
         <v>1</v>
       </c>
       <c r="K250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -11699,7 +11734,7 @@
         <v>0</v>
       </c>
       <c r="K257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L257" t="inlineStr">
         <is>
@@ -12007,7 +12042,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -12315,7 +12350,7 @@
         <v>1</v>
       </c>
       <c r="K271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -12623,7 +12658,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -12931,7 +12966,7 @@
         <v>1</v>
       </c>
       <c r="K285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -13239,7 +13274,7 @@
         <v>1</v>
       </c>
       <c r="K292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -13547,7 +13582,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -13620,7 +13655,7 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G301" t="n">
         <v>1</v>
@@ -13855,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -14163,7 +14198,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -14471,7 +14506,7 @@
         <v>1</v>
       </c>
       <c r="K320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -14619,7 +14654,12 @@
         <v>3</v>
       </c>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -14658,7 +14698,12 @@
         <v>3</v>
       </c>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -14697,7 +14742,12 @@
         <v>3</v>
       </c>
       <c r="C326" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -14736,7 +14786,12 @@
         <v>3</v>
       </c>
       <c r="C327" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -14759,7 +14814,7 @@
         <v>1</v>
       </c>
       <c r="K327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -14777,6 +14832,11 @@
       <c r="C328" t="n">
         <v>1</v>
       </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>5-cq25111501-1</t>
@@ -14816,6 +14876,11 @@
       <c r="C329" t="n">
         <v>2</v>
       </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>6-02/09</t>
@@ -14853,7 +14918,12 @@
         <v>3</v>
       </c>
       <c r="C330" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -15052,7 +15122,7 @@
         <v>1</v>
       </c>
       <c r="K334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -15360,7 +15430,7 @@
         <v>1</v>
       </c>
       <c r="K341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -15668,7 +15738,7 @@
         <v>1</v>
       </c>
       <c r="K348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -15976,7 +16046,7 @@
         <v>1</v>
       </c>
       <c r="K355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -16284,7 +16354,7 @@
         <v>1</v>
       </c>
       <c r="K362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
@@ -16592,7 +16662,7 @@
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -16900,7 +16970,7 @@
         <v>0</v>
       </c>
       <c r="K376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L376" t="inlineStr">
         <is>
@@ -17208,7 +17278,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -17516,7 +17586,7 @@
         <v>0</v>
       </c>
       <c r="K390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -17824,7 +17894,7 @@
         <v>1</v>
       </c>
       <c r="K397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -18132,7 +18202,7 @@
         <v>0</v>
       </c>
       <c r="K404" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
@@ -18440,7 +18510,7 @@
         <v>1</v>
       </c>
       <c r="K411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -18519,7 +18589,7 @@
         <v>3</v>
       </c>
       <c r="H413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I413" t="n">
         <v>1</v>
@@ -18748,7 +18818,7 @@
         <v>1</v>
       </c>
       <c r="K418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -19056,7 +19126,7 @@
         <v>0</v>
       </c>
       <c r="K425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
@@ -19364,7 +19434,7 @@
         <v>1</v>
       </c>
       <c r="K432" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -19672,7 +19742,7 @@
         <v>1</v>
       </c>
       <c r="K439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -19789,7 +19859,7 @@
         </is>
       </c>
       <c r="F442" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G442" t="n">
         <v>1</v>
@@ -19980,7 +20050,7 @@
         <v>1</v>
       </c>
       <c r="K446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L446" t="inlineStr">
         <is>
@@ -20288,7 +20358,7 @@
         <v>1</v>
       </c>
       <c r="K453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L453" t="inlineStr">
         <is>
@@ -20596,7 +20666,7 @@
         <v>0</v>
       </c>
       <c r="K460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -20904,7 +20974,7 @@
         <v>1</v>
       </c>
       <c r="K467" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L467" t="inlineStr">
         <is>
@@ -21212,7 +21282,7 @@
         <v>1</v>
       </c>
       <c r="K474" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L474" t="inlineStr">
         <is>
@@ -21520,7 +21590,7 @@
         <v>1</v>
       </c>
       <c r="K481" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L481" t="inlineStr">
         <is>
@@ -21828,7 +21898,7 @@
         <v>1</v>
       </c>
       <c r="K488" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
@@ -22136,7 +22206,7 @@
         <v>1</v>
       </c>
       <c r="K495" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L495" t="inlineStr">
         <is>
@@ -22444,7 +22514,7 @@
         <v>0</v>
       </c>
       <c r="K502" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L502" t="inlineStr">
         <is>
@@ -22752,7 +22822,7 @@
         <v>1</v>
       </c>
       <c r="K509" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L509" t="inlineStr">
         <is>
@@ -22902,6 +22972,11 @@
       <c r="C513" t="n">
         <v>2</v>
       </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E513" t="inlineStr">
         <is>
           <t>1-250906</t>
@@ -22941,6 +23016,11 @@
       <c r="C514" t="n">
         <v>2</v>
       </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E514" t="inlineStr">
         <is>
           <t>2-25c062101</t>
@@ -22980,6 +23060,11 @@
       <c r="C515" t="n">
         <v>1</v>
       </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E515" t="inlineStr">
         <is>
           <t>3-4/02/2020</t>
@@ -23019,6 +23104,11 @@
       <c r="C516" t="n">
         <v>2</v>
       </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>4-cq23120101-2</t>
@@ -23040,7 +23130,7 @@
         <v>1</v>
       </c>
       <c r="K516" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L516" t="inlineStr">
         <is>
@@ -23058,6 +23148,11 @@
       <c r="C517" t="n">
         <v>1</v>
       </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
       <c r="E517" t="inlineStr">
         <is>
           <t>5-cq25111501-1</t>
@@ -23095,7 +23190,12 @@
         <v>2</v>
       </c>
       <c r="C518" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -23134,7 +23234,12 @@
         <v>2</v>
       </c>
       <c r="C519" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -23333,7 +23438,7 @@
         <v>0</v>
       </c>
       <c r="K523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L523" t="inlineStr">
         <is>
